--- a/DOC/SBE_parameters.xlsx
+++ b/DOC/SBE_parameters.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00-GCOOS\00-MBON\SFER_CTD\01-CONVERT_WORKDIR\DOC\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021A6AC8-B52B-4AC3-AE4B-E9FC35621C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ufDV5O8+SXHt1P2yoHxSAjGlo2ejC35UsHnZhKzMnMc="/>
@@ -16,22 +25,30 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="D6">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABXNvf8gA
 Tuomo Saari    (2024-10-10 22:54:17)
 Manual: "Pressure data typically filtered with constant four times the scan rate, so check scan rate first!"</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mi6F6f5R9Et0dbvwKmdIlj1ch/+Mw=="/>
     </ext>
   </extLst>
@@ -46,46 +63,52 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>1)</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> only convert independent variables (can include descent rate to see plot, loop edit needed?)  </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>2)</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> Depth and sound vel (Misc. tab): apply sensible latitude to use if missing (check a .hex file)  </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>3)</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> Oxygen (misc tab): apply hysteresis. Tau correction can be applied at Dervice -step (not both!)</t>
     </r>
@@ -129,17 +152,18 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>SBE 9</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>plus</t>
     </r>
@@ -147,42 +171,43 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">SBE 19 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>plus</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>;19 plus</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>V2</t>
     </r>
@@ -199,17 +224,18 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>SBE 9</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>plus</t>
     </r>
@@ -220,42 +246,43 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">SBE 19 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>plus</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>;19 plus</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>V2</t>
     </r>
@@ -269,17 +296,18 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>SBE 9</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>plus</t>
     </r>
@@ -290,42 +318,43 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">SBE 19 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>plus</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>;19 plus</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>V2</t>
     </r>
@@ -346,39 +375,44 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Density, depth, salinity, sound velocity, </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>descent rate</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">, oxygen.
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>Manual about oxygen</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">: " (if input file contains pressure, temperature, and either
 conductivity or salinity, and has not been averaged into pressure or
@@ -388,16 +422,18 @@
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
         <b/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>Manual, depth:</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> Add correct latitude (look at the data) to use when NMEA latitude not available. This is on the Miscellaneous tab.</t>
     </r>
@@ -409,44 +445,52 @@
     <t>checked from Seasoft Data Processing Manual</t>
   </si>
   <si>
-    <t>My guess for Hogarth (SBE 25plus)</t>
+    <t>My guess for Hogarth (SBE 25plus) OBS! This is sample rate dependent!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -454,7 +498,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -470,60 +514,51 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="164" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -713,26 +748,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="31.78"/>
-    <col customWidth="1" min="2" max="2" width="18.44"/>
-    <col customWidth="1" min="3" max="3" width="16.22"/>
-    <col customWidth="1" min="4" max="4" width="15.33"/>
-    <col customWidth="1" min="5" max="5" width="15.89"/>
-    <col customWidth="1" min="6" max="6" width="11.22"/>
-    <col customWidth="1" min="8" max="8" width="14.33"/>
+    <col min="1" max="1" width="31.796875" customWidth="1"/>
+    <col min="2" max="2" width="18.3984375" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" customWidth="1"/>
+    <col min="4" max="4" width="15.296875" customWidth="1"/>
+    <col min="5" max="5" width="15.8984375" customWidth="1"/>
+    <col min="6" max="6" width="11.19921875" customWidth="1"/>
+    <col min="8" max="8" width="14.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -740,334 +775,332 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
         <v>0.15</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.03</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <v>0.03</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
         <v>0.03</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="3">
         <v>0.03</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>0.5</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <v>0.5</v>
       </c>
-      <c r="D5" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="4">
         <v>0.1</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <v>0.1</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="4">
         <v>0.5</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="8">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="5">
-        <v>0.085</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0.085</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="B7" s="3">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="C7" s="3">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="D7" s="3">
         <v>0.25</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5">
-        <v>0.073</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5" t="s">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="3">
         <v>0.5</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="3">
         <v>0.1</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="s">
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="7">
+      <c r="B11" s="3"/>
+      <c r="C11" s="4">
         <v>0.1</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="9" t="s">
+      <c r="D11" s="3"/>
+      <c r="E11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="5">
-        <v>0.0625</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="B12" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="s">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="3"/>
+      <c r="C14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="3"/>
+      <c r="C16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="23">
-      <c r="A23" s="11" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="13" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="9" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>